--- a/feature/refactor-validateur-tab/ig/ValueSet-sas-valueset-typeidentifiant.xlsx
+++ b/feature/refactor-validateur-tab/ig/ValueSet-sas-valueset-typeidentifiant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T14:41:42+00:00</t>
+    <t>2026-07-13T16:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
